--- a/data/trans_orig/IP25A_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6272</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4711</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8886</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45583</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42843</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47672</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51355</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47180</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53814</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>46513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50012</t>
+          <t>42953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57434</t>
+          <t>48568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106007</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109856</t>
+          <t>95197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21683</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15155</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29763</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19166</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13227</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26584</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>40013</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57144</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>135839</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>127759</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>142367</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>136197</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>128779</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142136</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>156604</t>
+          <t>123591</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147046</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164309</t>
+          <t>129322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>292801</t>
+          <t>259429</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280773</t>
+          <t>250023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>302797</t>
+          <t>268622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>155363</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>155363</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>155363</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>141921</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>141921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>141921</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>337917</t>
+          <t>299442</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>337917</t>
+          <t>299442</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>337917</t>
+          <t>299442</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44718</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>58949</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>46166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81459</t>
+          <t>72258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>169825</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159445</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>178307</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>139419</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127606</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148618</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,91%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180717</t>
+          <t>145200</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169661</t>
+          <t>135905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189228</t>
+          <t>153012</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>320137</t>
+          <t>315026</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303355</t>
+          <t>301717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334360</t>
+          <t>327809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40494</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30951</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54101</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32947</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22971</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44815</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41526</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>41799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>59678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91115</t>
+          <t>88212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>250645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>237038</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>260188</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>237489</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>225621</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>247465</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>262496</t>
+          <t>218827</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248723</t>
+          <t>209648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>227710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>499985</t>
+          <t>469472</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>483344</t>
+          <t>454374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>516118</t>
+          <t>482908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>291139</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>291139</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>291139</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>270436</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>270436</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>270436</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304022</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304022</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304022</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>574459</t>
+          <t>542586</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>574459</t>
+          <t>542586</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>574459</t>
+          <t>542586</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,62 +2092,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>96010</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>81248</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>112983</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89730</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>72364</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107420</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87401</t>
+          <t>71183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123075</t>
+          <t>99093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171524</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223073</t>
+          <t>204211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -2205,67 +2205,67 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>601891</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>584918</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>616653</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>564459</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>546769</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>581825</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>654469</t>
+          <t>534132</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635719</t>
+          <t>518975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>671393</t>
+          <t>546885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1218928</t>
+          <t>1136024</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1189910</t>
+          <t>1111759</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1241459</t>
+          <t>1156603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
